--- a/DATA_QUALITY.xlsx
+++ b/DATA_QUALITY.xlsx
@@ -82248,7 +82248,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T17:58:26.052168+00:00</t>
+          <t>2026-10-18T20:02:23.655186+00:00</t>
         </is>
       </c>
     </row>
@@ -82448,7 +82448,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>2b9bd4ef427437f7c79678cc</t>
+          <t>33cc3a616435735e314b5eb1</t>
         </is>
       </c>
     </row>
@@ -82544,7 +82544,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T17:58:26.812400+00:00</t>
+          <t>2026-10-18T20:02:24.333960+00:00</t>
         </is>
       </c>
     </row>
@@ -82568,7 +82568,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T17:58:26.052168+00:00</t>
+          <t>2026-10-18T20:02:23.655186+00:00</t>
         </is>
       </c>
     </row>
@@ -82664,7 +82664,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T17:58:27.092726+00:00</t>
+          <t>2026-10-18T20:02:24.641961+00:00</t>
         </is>
       </c>
     </row>
@@ -82760,7 +82760,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>2026-10-17T17:58:27.410376+00:00</t>
+          <t>2026-10-18T20:02:24.960971+00:00</t>
         </is>
       </c>
     </row>

--- a/DATA_QUALITY.xlsx
+++ b/DATA_QUALITY.xlsx
@@ -82248,7 +82248,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T20:02:23.655186+00:00</t>
+          <t>2026-10-18T21:11:49.395606+00:00</t>
         </is>
       </c>
     </row>
@@ -82448,7 +82448,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>33cc3a616435735e314b5eb1</t>
+          <t>5fb4c047808c71233216b53a</t>
         </is>
       </c>
     </row>
@@ -82544,7 +82544,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T20:02:24.333960+00:00</t>
+          <t>2026-10-18T21:11:50.125862+00:00</t>
         </is>
       </c>
     </row>
@@ -82568,7 +82568,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T20:02:23.655186+00:00</t>
+          <t>2026-10-18T21:11:49.395606+00:00</t>
         </is>
       </c>
     </row>
@@ -82664,7 +82664,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T20:02:24.641961+00:00</t>
+          <t>2026-10-18T21:11:50.456861+00:00</t>
         </is>
       </c>
     </row>
@@ -82760,7 +82760,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T20:02:24.960971+00:00</t>
+          <t>2026-10-18T21:11:50.847856+00:00</t>
         </is>
       </c>
     </row>

--- a/DATA_QUALITY.xlsx
+++ b/DATA_QUALITY.xlsx
@@ -82248,7 +82248,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T21:11:49.395606+00:00</t>
+          <t>2026-10-19T03:28:18.346528+00:00</t>
         </is>
       </c>
     </row>
@@ -82448,7 +82448,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>5fb4c047808c71233216b53a</t>
+          <t>2aad0c28d1757a95e5a58a45</t>
         </is>
       </c>
     </row>
@@ -82544,7 +82544,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T21:11:50.125862+00:00</t>
+          <t>2026-10-19T03:28:19.129203+00:00</t>
         </is>
       </c>
     </row>
@@ -82568,7 +82568,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T21:11:49.395606+00:00</t>
+          <t>2026-10-19T03:28:18.346528+00:00</t>
         </is>
       </c>
     </row>
@@ -82664,7 +82664,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T21:11:50.456861+00:00</t>
+          <t>2026-10-19T03:28:19.439199+00:00</t>
         </is>
       </c>
     </row>
@@ -82760,7 +82760,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>2026-10-18T21:11:50.847856+00:00</t>
+          <t>2026-10-19T03:28:19.820203+00:00</t>
         </is>
       </c>
     </row>

--- a/DATA_QUALITY.xlsx
+++ b/DATA_QUALITY.xlsx
@@ -82248,7 +82248,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T03:28:18.346528+00:00</t>
+          <t>2026-10-19T05:48:09.843244+00:00</t>
         </is>
       </c>
     </row>
@@ -82448,7 +82448,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>2aad0c28d1757a95e5a58a45</t>
+          <t>a484bfa6924c5c24209884e9</t>
         </is>
       </c>
     </row>
@@ -82544,7 +82544,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T03:28:19.129203+00:00</t>
+          <t>2026-10-19T05:48:10.674608+00:00</t>
         </is>
       </c>
     </row>
@@ -82568,7 +82568,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T03:28:18.346528+00:00</t>
+          <t>2026-10-19T05:48:09.843244+00:00</t>
         </is>
       </c>
     </row>
@@ -82664,7 +82664,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T03:28:19.439199+00:00</t>
+          <t>2026-10-19T05:48:10.975712+00:00</t>
         </is>
       </c>
     </row>
@@ -82760,7 +82760,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19T03:28:19.820203+00:00</t>
+          <t>2026-10-19T05:48:11.315947+00:00</t>
         </is>
       </c>
     </row>
